--- a/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK ANTLERLESS GENERAL SEASON ANY LEGAL WEAPON.xlsx
+++ b/processed_data/hard_data_exports/hunt_tables/2026/CLEAN_XLXS_STAGED/2026 ELK ANTLERLESS GENERAL SEASON ANY LEGAL WEAPON.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O99"/>
+  <dimension ref="A1:P99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -577,10 +577,15 @@
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>Average Age Harvested (previous hunting season)</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
+          <t>Average Harvest Age</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Current Age (3-Yr Avg)</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Avg Days Hunted (previous hunting season)</t>
         </is>
@@ -653,7 +658,8 @@
         </is>
       </c>
       <c r="N2" s="2" t="inlineStr"/>
-      <c r="O2" s="2" t="inlineStr">
+      <c r="O2" t="inlineStr"/>
+      <c r="P2" s="2" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -726,7 +732,8 @@
         </is>
       </c>
       <c r="N3" s="3" t="inlineStr"/>
-      <c r="O3" s="3" t="inlineStr">
+      <c r="O3" t="inlineStr"/>
+      <c r="P3" s="3" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -799,7 +806,8 @@
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr"/>
-      <c r="O4" s="2" t="inlineStr">
+      <c r="O4" t="inlineStr"/>
+      <c r="P4" s="2" t="inlineStr">
         <is>
           <t>15</t>
         </is>
@@ -876,7 +884,8 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="O5" s="3" t="inlineStr">
+      <c r="O5" t="inlineStr"/>
+      <c r="P5" s="3" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -949,7 +958,8 @@
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr"/>
-      <c r="O6" s="2" t="inlineStr">
+      <c r="O6" t="inlineStr"/>
+      <c r="P6" s="2" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -1022,7 +1032,8 @@
         </is>
       </c>
       <c r="N7" s="3" t="inlineStr"/>
-      <c r="O7" s="3" t="inlineStr">
+      <c r="O7" t="inlineStr"/>
+      <c r="P7" s="3" t="inlineStr">
         <is>
           <t>9.5</t>
         </is>
@@ -1095,7 +1106,8 @@
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr"/>
-      <c r="O8" s="2" t="inlineStr">
+      <c r="O8" t="inlineStr"/>
+      <c r="P8" s="2" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -1168,7 +1180,8 @@
         </is>
       </c>
       <c r="N9" s="3" t="inlineStr"/>
-      <c r="O9" s="3" t="inlineStr">
+      <c r="O9" t="inlineStr"/>
+      <c r="P9" s="3" t="inlineStr">
         <is>
           <t>10.8</t>
         </is>
@@ -1245,7 +1258,8 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="O10" t="inlineStr"/>
+      <c r="P10" s="2" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -1322,7 +1336,8 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="O11" s="3" t="inlineStr">
+      <c r="O11" t="inlineStr"/>
+      <c r="P11" s="3" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -1399,7 +1414,8 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="O12" s="2" t="inlineStr">
+      <c r="O12" t="inlineStr"/>
+      <c r="P12" s="2" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -1476,7 +1492,8 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="O13" s="3" t="inlineStr">
+      <c r="O13" t="inlineStr"/>
+      <c r="P13" s="3" t="inlineStr">
         <is>
           <t>7.3</t>
         </is>
@@ -1553,7 +1570,8 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="O14" s="2" t="inlineStr">
+      <c r="O14" t="inlineStr"/>
+      <c r="P14" s="2" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -1626,7 +1644,8 @@
         </is>
       </c>
       <c r="N15" s="3" t="inlineStr"/>
-      <c r="O15" s="3" t="inlineStr">
+      <c r="O15" t="inlineStr"/>
+      <c r="P15" s="3" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -1703,7 +1722,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="O16" t="inlineStr"/>
+      <c r="P16" s="2" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -1780,7 +1800,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O17" s="3" t="inlineStr">
+      <c r="O17" t="inlineStr"/>
+      <c r="P17" s="3" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -1853,7 +1874,8 @@
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr"/>
-      <c r="O18" s="2" t="inlineStr">
+      <c r="O18" t="inlineStr"/>
+      <c r="P18" s="2" t="inlineStr">
         <is>
           <t>7.6</t>
         </is>
@@ -1926,7 +1948,8 @@
         </is>
       </c>
       <c r="N19" s="3" t="inlineStr"/>
-      <c r="O19" s="3" t="inlineStr">
+      <c r="O19" t="inlineStr"/>
+      <c r="P19" s="3" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
@@ -2003,7 +2026,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O20" s="2" t="inlineStr">
+      <c r="O20" t="inlineStr"/>
+      <c r="P20" s="2" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -2080,7 +2104,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O21" s="3" t="inlineStr">
+      <c r="O21" t="inlineStr"/>
+      <c r="P21" s="3" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -2157,7 +2182,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
+      <c r="O22" t="inlineStr"/>
+      <c r="P22" s="2" t="inlineStr">
         <is>
           <t>6.1</t>
         </is>
@@ -2230,7 +2256,8 @@
         </is>
       </c>
       <c r="N23" s="3" t="inlineStr"/>
-      <c r="O23" s="3" t="inlineStr">
+      <c r="O23" t="inlineStr"/>
+      <c r="P23" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -2307,7 +2334,8 @@
           <t>7.5</t>
         </is>
       </c>
-      <c r="O24" s="2" t="inlineStr">
+      <c r="O24" t="inlineStr"/>
+      <c r="P24" s="2" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -2384,7 +2412,8 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="O25" s="3" t="inlineStr">
+      <c r="O25" t="inlineStr"/>
+      <c r="P25" s="3" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -2461,7 +2490,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O26" s="2" t="inlineStr">
+      <c r="O26" t="inlineStr"/>
+      <c r="P26" s="2" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -2538,7 +2568,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O27" s="3" t="inlineStr">
+      <c r="O27" t="inlineStr"/>
+      <c r="P27" s="3" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -2611,7 +2642,8 @@
         </is>
       </c>
       <c r="N28" s="2" t="inlineStr"/>
-      <c r="O28" s="2" t="inlineStr">
+      <c r="O28" t="inlineStr"/>
+      <c r="P28" s="2" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -2684,7 +2716,8 @@
         </is>
       </c>
       <c r="N29" s="3" t="inlineStr"/>
-      <c r="O29" s="3" t="inlineStr">
+      <c r="O29" t="inlineStr"/>
+      <c r="P29" s="3" t="inlineStr">
         <is>
           <t>5.3</t>
         </is>
@@ -2761,7 +2794,8 @@
           <t>7.6</t>
         </is>
       </c>
-      <c r="O30" s="2" t="inlineStr">
+      <c r="O30" t="inlineStr"/>
+      <c r="P30" s="2" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
@@ -2838,7 +2872,8 @@
           <t>5.5</t>
         </is>
       </c>
-      <c r="O31" s="3" t="inlineStr">
+      <c r="O31" t="inlineStr"/>
+      <c r="P31" s="3" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
@@ -2911,7 +2946,8 @@
         </is>
       </c>
       <c r="N32" s="2" t="inlineStr"/>
-      <c r="O32" s="2" t="inlineStr">
+      <c r="O32" t="inlineStr"/>
+      <c r="P32" s="2" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -2984,7 +3020,8 @@
         </is>
       </c>
       <c r="N33" s="3" t="inlineStr"/>
-      <c r="O33" s="3" t="inlineStr">
+      <c r="O33" t="inlineStr"/>
+      <c r="P33" s="3" t="inlineStr">
         <is>
           <t>3.3</t>
         </is>
@@ -3057,7 +3094,8 @@
         </is>
       </c>
       <c r="N34" s="2" t="inlineStr"/>
-      <c r="O34" s="2" t="inlineStr">
+      <c r="O34" t="inlineStr"/>
+      <c r="P34" s="2" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -3134,7 +3172,8 @@
           <t>6.9</t>
         </is>
       </c>
-      <c r="O35" s="3" t="inlineStr">
+      <c r="O35" t="inlineStr"/>
+      <c r="P35" s="3" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -3211,7 +3250,8 @@
           <t>6.9</t>
         </is>
       </c>
-      <c r="O36" s="2" t="inlineStr">
+      <c r="O36" t="inlineStr"/>
+      <c r="P36" s="2" t="inlineStr">
         <is>
           <t>2.5</t>
         </is>
@@ -3288,7 +3328,8 @@
           <t>6.9</t>
         </is>
       </c>
-      <c r="O37" s="3" t="inlineStr">
+      <c r="O37" t="inlineStr"/>
+      <c r="P37" s="3" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -3365,7 +3406,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O38" s="2" t="inlineStr">
+      <c r="O38" t="inlineStr"/>
+      <c r="P38" s="2" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3442,7 +3484,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O39" s="3" t="inlineStr">
+      <c r="O39" t="inlineStr"/>
+      <c r="P39" s="3" t="inlineStr">
         <is>
           <t>5.6</t>
         </is>
@@ -3511,7 +3554,8 @@
           <t>6.4</t>
         </is>
       </c>
-      <c r="O40" s="2" t="inlineStr">
+      <c r="O40" t="inlineStr"/>
+      <c r="P40" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
@@ -3588,7 +3632,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O41" s="3" t="inlineStr">
+      <c r="O41" t="inlineStr"/>
+      <c r="P41" s="3" t="inlineStr">
         <is>
           <t>5.5</t>
         </is>
@@ -3665,7 +3710,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O42" s="2" t="inlineStr">
+      <c r="O42" t="inlineStr"/>
+      <c r="P42" s="2" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -3742,7 +3788,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O43" s="3" t="inlineStr">
+      <c r="O43" t="inlineStr"/>
+      <c r="P43" s="3" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -3819,7 +3866,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O44" s="2" t="inlineStr">
+      <c r="O44" t="inlineStr"/>
+      <c r="P44" s="2" t="inlineStr">
         <is>
           <t>6.4</t>
         </is>
@@ -3896,7 +3944,8 @@
           <t>8.1</t>
         </is>
       </c>
-      <c r="O45" s="3" t="inlineStr">
+      <c r="O45" t="inlineStr"/>
+      <c r="P45" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -3969,7 +4018,8 @@
         </is>
       </c>
       <c r="N46" s="2" t="inlineStr"/>
-      <c r="O46" s="2" t="inlineStr">
+      <c r="O46" t="inlineStr"/>
+      <c r="P46" s="2" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -4043,10 +4093,11 @@
       </c>
       <c r="N47" s="3" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="O47" s="3" t="inlineStr">
+          <t>5</t>
+        </is>
+      </c>
+      <c r="O47" t="inlineStr"/>
+      <c r="P47" s="3" t="inlineStr">
         <is>
           <t>8.5</t>
         </is>
@@ -4123,7 +4174,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="O48" s="2" t="inlineStr">
+      <c r="O48" t="inlineStr"/>
+      <c r="P48" s="2" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -4200,7 +4252,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="O49" s="3" t="inlineStr">
+      <c r="O49" t="inlineStr"/>
+      <c r="P49" s="3" t="inlineStr">
         <is>
           <t>4.5</t>
         </is>
@@ -4277,7 +4330,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="O50" s="2" t="inlineStr">
+      <c r="O50" t="inlineStr"/>
+      <c r="P50" s="2" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -4354,7 +4408,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="O51" s="3" t="inlineStr">
+      <c r="O51" t="inlineStr"/>
+      <c r="P51" s="3" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -4427,7 +4482,8 @@
         </is>
       </c>
       <c r="N52" s="2" t="inlineStr"/>
-      <c r="O52" s="2" t="inlineStr">
+      <c r="O52" t="inlineStr"/>
+      <c r="P52" s="2" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -4504,7 +4560,8 @@
           <t>5.5</t>
         </is>
       </c>
-      <c r="O53" s="3" t="inlineStr">
+      <c r="O53" t="inlineStr"/>
+      <c r="P53" s="3" t="inlineStr">
         <is>
           <t>8.2</t>
         </is>
@@ -4577,7 +4634,8 @@
         </is>
       </c>
       <c r="N54" s="2" t="inlineStr"/>
-      <c r="O54" s="2" t="inlineStr">
+      <c r="O54" t="inlineStr"/>
+      <c r="P54" s="2" t="inlineStr">
         <is>
           <t>4.1</t>
         </is>
@@ -4654,7 +4712,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O55" s="3" t="inlineStr">
+      <c r="O55" t="inlineStr"/>
+      <c r="P55" s="3" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -4731,7 +4790,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O56" s="2" t="inlineStr">
+      <c r="O56" t="inlineStr"/>
+      <c r="P56" s="2" t="inlineStr">
         <is>
           <t>3.2</t>
         </is>
@@ -4808,7 +4868,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O57" s="3" t="inlineStr">
+      <c r="O57" t="inlineStr"/>
+      <c r="P57" s="3" t="inlineStr">
         <is>
           <t>1.8</t>
         </is>
@@ -4881,7 +4942,8 @@
         </is>
       </c>
       <c r="N58" s="2" t="inlineStr"/>
-      <c r="O58" s="2" t="inlineStr">
+      <c r="O58" t="inlineStr"/>
+      <c r="P58" s="2" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -4946,7 +5008,8 @@
       <c r="L59" s="3" t="inlineStr"/>
       <c r="M59" s="3" t="inlineStr"/>
       <c r="N59" s="3" t="inlineStr"/>
-      <c r="O59" s="3" t="inlineStr">
+      <c r="O59" t="inlineStr"/>
+      <c r="P59" s="3" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -5023,7 +5086,8 @@
           <t>7.2</t>
         </is>
       </c>
-      <c r="O60" s="2" t="inlineStr">
+      <c r="O60" t="inlineStr"/>
+      <c r="P60" s="2" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -5100,7 +5164,8 @@
           <t>7.7</t>
         </is>
       </c>
-      <c r="O61" s="3" t="inlineStr">
+      <c r="O61" t="inlineStr"/>
+      <c r="P61" s="3" t="inlineStr">
         <is>
           <t>14.5</t>
         </is>
@@ -5177,7 +5242,8 @@
           <t>5</t>
         </is>
       </c>
-      <c r="O62" s="2" t="inlineStr">
+      <c r="O62" t="inlineStr"/>
+      <c r="P62" s="2" t="inlineStr">
         <is>
           <t>4.9</t>
         </is>
@@ -5238,7 +5304,8 @@
           <t>6.5</t>
         </is>
       </c>
-      <c r="O63" s="3" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+      <c r="P63" s="3" t="inlineStr"/>
     </row>
     <row r="64" ht="42" customHeight="1">
       <c r="A64" s="2" t="inlineStr">
@@ -5291,7 +5358,8 @@
       <c r="L64" s="2" t="inlineStr"/>
       <c r="M64" s="2" t="inlineStr"/>
       <c r="N64" s="2" t="inlineStr"/>
-      <c r="O64" s="2" t="inlineStr">
+      <c r="O64" t="inlineStr"/>
+      <c r="P64" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
@@ -5368,7 +5436,8 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="O65" s="3" t="inlineStr">
+      <c r="O65" t="inlineStr"/>
+      <c r="P65" s="3" t="inlineStr">
         <is>
           <t>5.7</t>
         </is>
@@ -5445,7 +5514,8 @@
           <t>9.1</t>
         </is>
       </c>
-      <c r="O66" s="2" t="inlineStr">
+      <c r="O66" t="inlineStr"/>
+      <c r="P66" s="2" t="inlineStr">
         <is>
           <t>3.5</t>
         </is>
@@ -5522,7 +5592,8 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="O67" s="3" t="inlineStr">
+      <c r="O67" t="inlineStr"/>
+      <c r="P67" s="3" t="inlineStr">
         <is>
           <t>4</t>
         </is>
@@ -5599,7 +5670,8 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="O68" s="2" t="inlineStr">
+      <c r="O68" t="inlineStr"/>
+      <c r="P68" s="2" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
@@ -5664,7 +5736,8 @@
       <c r="L69" s="3" t="inlineStr"/>
       <c r="M69" s="3" t="inlineStr"/>
       <c r="N69" s="3" t="inlineStr"/>
-      <c r="O69" s="3" t="inlineStr">
+      <c r="O69" t="inlineStr"/>
+      <c r="P69" s="3" t="inlineStr">
         <is>
           <t>3.6</t>
         </is>
@@ -5737,7 +5810,8 @@
         </is>
       </c>
       <c r="N70" s="2" t="inlineStr"/>
-      <c r="O70" s="2" t="inlineStr">
+      <c r="O70" t="inlineStr"/>
+      <c r="P70" s="2" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
@@ -5810,7 +5884,8 @@
         </is>
       </c>
       <c r="N71" s="3" t="inlineStr"/>
-      <c r="O71" s="3" t="inlineStr">
+      <c r="O71" t="inlineStr"/>
+      <c r="P71" s="3" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
@@ -5887,7 +5962,8 @@
           <t>7.4</t>
         </is>
       </c>
-      <c r="O72" s="2" t="inlineStr">
+      <c r="O72" t="inlineStr"/>
+      <c r="P72" s="2" t="inlineStr">
         <is>
           <t>10.4</t>
         </is>
@@ -5960,7 +6036,8 @@
         </is>
       </c>
       <c r="N73" s="3" t="inlineStr"/>
-      <c r="O73" s="3" t="inlineStr">
+      <c r="O73" t="inlineStr"/>
+      <c r="P73" s="3" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
@@ -6037,7 +6114,8 @@
           <t>6.2</t>
         </is>
       </c>
-      <c r="O74" s="2" t="inlineStr">
+      <c r="O74" t="inlineStr"/>
+      <c r="P74" s="2" t="inlineStr">
         <is>
           <t>6.2</t>
         </is>
@@ -6114,7 +6192,8 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="O75" s="3" t="inlineStr">
+      <c r="O75" t="inlineStr"/>
+      <c r="P75" s="3" t="inlineStr">
         <is>
           <t>5.1</t>
         </is>
@@ -6191,7 +6270,8 @@
           <t>5.2</t>
         </is>
       </c>
-      <c r="O76" s="2" t="inlineStr">
+      <c r="O76" t="inlineStr"/>
+      <c r="P76" s="2" t="inlineStr">
         <is>
           <t>7.5</t>
         </is>
@@ -6268,7 +6348,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O77" s="3" t="inlineStr">
+      <c r="O77" t="inlineStr"/>
+      <c r="P77" s="3" t="inlineStr">
         <is>
           <t>5.9</t>
         </is>
@@ -6345,7 +6426,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O78" s="2" t="inlineStr">
+      <c r="O78" t="inlineStr"/>
+      <c r="P78" s="2" t="inlineStr">
         <is>
           <t>6.3</t>
         </is>
@@ -6422,7 +6504,8 @@
           <t>7</t>
         </is>
       </c>
-      <c r="O79" s="3" t="inlineStr">
+      <c r="O79" t="inlineStr"/>
+      <c r="P79" s="3" t="inlineStr">
         <is>
           <t>4.4</t>
         </is>
@@ -6499,7 +6582,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O80" s="2" t="inlineStr">
+      <c r="O80" t="inlineStr"/>
+      <c r="P80" s="2" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -6576,7 +6660,8 @@
           <t>8.1</t>
         </is>
       </c>
-      <c r="O81" s="3" t="inlineStr">
+      <c r="O81" t="inlineStr"/>
+      <c r="P81" s="3" t="inlineStr">
         <is>
           <t>4.7</t>
         </is>
@@ -6649,7 +6734,8 @@
         </is>
       </c>
       <c r="N82" s="2" t="inlineStr"/>
-      <c r="O82" s="2" t="inlineStr">
+      <c r="O82" t="inlineStr"/>
+      <c r="P82" s="2" t="inlineStr">
         <is>
           <t>7.8</t>
         </is>
@@ -6710,7 +6796,8 @@
           <t>5.7</t>
         </is>
       </c>
-      <c r="O83" s="3" t="inlineStr"/>
+      <c r="O83" t="inlineStr"/>
+      <c r="P83" s="3" t="inlineStr"/>
     </row>
     <row r="84" ht="42" customHeight="1">
       <c r="A84" s="2" t="inlineStr">
@@ -6779,7 +6866,8 @@
         </is>
       </c>
       <c r="N84" s="2" t="inlineStr"/>
-      <c r="O84" s="2" t="inlineStr">
+      <c r="O84" t="inlineStr"/>
+      <c r="P84" s="2" t="inlineStr">
         <is>
           <t>2.8</t>
         </is>
@@ -6852,7 +6940,8 @@
         </is>
       </c>
       <c r="N85" s="3" t="inlineStr"/>
-      <c r="O85" s="3" t="inlineStr">
+      <c r="O85" t="inlineStr"/>
+      <c r="P85" s="3" t="inlineStr">
         <is>
           <t>2.9</t>
         </is>
@@ -6925,7 +7014,8 @@
         </is>
       </c>
       <c r="N86" s="2" t="inlineStr"/>
-      <c r="O86" s="2" t="inlineStr">
+      <c r="O86" t="inlineStr"/>
+      <c r="P86" s="2" t="inlineStr">
         <is>
           <t>11.3</t>
         </is>
@@ -6998,7 +7088,8 @@
         </is>
       </c>
       <c r="N87" s="3" t="inlineStr"/>
-      <c r="O87" s="3" t="inlineStr">
+      <c r="O87" t="inlineStr"/>
+      <c r="P87" s="3" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -7071,7 +7162,8 @@
         </is>
       </c>
       <c r="N88" s="2" t="inlineStr"/>
-      <c r="O88" s="2" t="inlineStr">
+      <c r="O88" t="inlineStr"/>
+      <c r="P88" s="2" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -7144,7 +7236,8 @@
         </is>
       </c>
       <c r="N89" s="3" t="inlineStr"/>
-      <c r="O89" s="3" t="inlineStr">
+      <c r="O89" t="inlineStr"/>
+      <c r="P89" s="3" t="inlineStr">
         <is>
           <t>6.5</t>
         </is>
@@ -7216,8 +7309,13 @@
           <t>82.6</t>
         </is>
       </c>
-      <c r="N90" s="2" t="inlineStr"/>
-      <c r="O90" s="2" t="inlineStr">
+      <c r="N90" s="2" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="O90" t="inlineStr"/>
+      <c r="P90" s="2" t="inlineStr">
         <is>
           <t>3.1</t>
         </is>
@@ -7290,7 +7388,8 @@
         </is>
       </c>
       <c r="N91" s="3" t="inlineStr"/>
-      <c r="O91" s="3" t="inlineStr">
+      <c r="O91" t="inlineStr"/>
+      <c r="P91" s="3" t="inlineStr">
         <is>
           <t>3.4</t>
         </is>
@@ -7362,8 +7461,13 @@
           <t>62.5</t>
         </is>
       </c>
-      <c r="N92" s="2" t="inlineStr"/>
-      <c r="O92" s="2" t="inlineStr">
+      <c r="N92" s="2" t="inlineStr">
+        <is>
+          <t>4.8</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr"/>
+      <c r="P92" s="2" t="inlineStr">
         <is>
           <t>2.1</t>
         </is>
@@ -7436,7 +7540,8 @@
         </is>
       </c>
       <c r="N93" s="3" t="inlineStr"/>
-      <c r="O93" s="3" t="inlineStr">
+      <c r="O93" t="inlineStr"/>
+      <c r="P93" s="3" t="inlineStr">
         <is>
           <t>5.4</t>
         </is>
@@ -7509,7 +7614,8 @@
         </is>
       </c>
       <c r="N94" s="2" t="inlineStr"/>
-      <c r="O94" s="2" t="inlineStr">
+      <c r="O94" t="inlineStr"/>
+      <c r="P94" s="2" t="inlineStr">
         <is>
           <t>7.7</t>
         </is>
@@ -7582,7 +7688,8 @@
         </is>
       </c>
       <c r="N95" s="3" t="inlineStr"/>
-      <c r="O95" s="3" t="inlineStr">
+      <c r="O95" t="inlineStr"/>
+      <c r="P95" s="3" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -7655,7 +7762,8 @@
         </is>
       </c>
       <c r="N96" s="2" t="inlineStr"/>
-      <c r="O96" s="2" t="inlineStr">
+      <c r="O96" t="inlineStr"/>
+      <c r="P96" s="2" t="inlineStr">
         <is>
           <t>4.2</t>
         </is>
@@ -7727,8 +7835,13 @@
           <t>61.3</t>
         </is>
       </c>
-      <c r="N97" s="3" t="inlineStr"/>
-      <c r="O97" s="3" t="inlineStr">
+      <c r="N97" s="3" t="inlineStr">
+        <is>
+          <t>7.9</t>
+        </is>
+      </c>
+      <c r="O97" t="inlineStr"/>
+      <c r="P97" s="3" t="inlineStr">
         <is>
           <t>2.2</t>
         </is>
@@ -7800,8 +7913,13 @@
           <t>60</t>
         </is>
       </c>
-      <c r="N98" s="2" t="inlineStr"/>
-      <c r="O98" s="2" t="inlineStr">
+      <c r="N98" s="2" t="inlineStr">
+        <is>
+          <t>8.3</t>
+        </is>
+      </c>
+      <c r="O98" t="inlineStr"/>
+      <c r="P98" s="2" t="inlineStr">
         <is>
           <t>3.8</t>
         </is>
@@ -7875,10 +7993,11 @@
       </c>
       <c r="N99" s="3" t="inlineStr">
         <is>
-          <t>2.3</t>
-        </is>
-      </c>
-      <c r="O99" s="3" t="inlineStr">
+          <t>9.1</t>
+        </is>
+      </c>
+      <c r="O99" t="inlineStr"/>
+      <c r="P99" s="3" t="inlineStr">
         <is>
           <t>4.3</t>
         </is>
